--- a/New_Outputs/Receptor_Group_Means.xlsx
+++ b/New_Outputs/Receptor_Group_Means.xlsx
@@ -561,7 +561,7 @@
         <v>0.3610828957109403</v>
       </c>
       <c r="P2">
-        <v>0.6317916594221523</v>
+        <v>0.4300553464550183</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -661,7 +661,7 @@
         <v>0.4837161122704481</v>
       </c>
       <c r="P4">
-        <v>0.6317916594221523</v>
+        <v>0.4655306964163227</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -711,7 +711,7 @@
         <v>0.4314946151969649</v>
       </c>
       <c r="P5">
-        <v>0.6911994563077999</v>
+        <v>0.6548205375547578</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -761,7 +761,7 @@
         <v>0.3459835068001251</v>
       </c>
       <c r="P6">
-        <v>0.6911994563077999</v>
+        <v>0.5828689709871098</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -811,7 +811,7 @@
         <v>0.3358414212353621</v>
       </c>
       <c r="P7">
-        <v>0.6198964654593174</v>
+        <v>0.2283829083271169</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -861,7 +861,7 @@
         <v>0.3760000486147377</v>
       </c>
       <c r="P8">
-        <v>0.6317916594221523</v>
+        <v>0.4193680872342135</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -911,7 +911,7 @@
         <v>0.2774205367524811</v>
       </c>
       <c r="P9">
-        <v>0.6156364835208624</v>
+        <v>0.1944115211118513</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -961,7 +961,7 @@
         <v>0.3157421861829662</v>
       </c>
       <c r="P10">
-        <v>0.6911994563077999</v>
+        <v>0.57127638098602</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -1011,7 +1011,7 @@
         <v>0.2069273538910608</v>
       </c>
       <c r="P11">
-        <v>0.6317916594221523</v>
+        <v>0.4310342829980617</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -1061,7 +1061,7 @@
         <v>0.239338320924609</v>
       </c>
       <c r="P12">
-        <v>0.3004723666655043</v>
+        <v>0.06325734035063249</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -1111,7 +1111,7 @@
         <v>0.2058564377680289</v>
       </c>
       <c r="P13">
-        <v>0.09231190590427386</v>
+        <v>0.01457556409014851</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -1161,7 +1161,7 @@
         <v>0.2828338957028231</v>
       </c>
       <c r="P14">
-        <v>0.09231190590427386</v>
+        <v>0.01436275972452762</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -1211,7 +1211,7 @@
         <v>0.3785177483661485</v>
       </c>
       <c r="P15">
-        <v>0.6317916594221523</v>
+        <v>0.3175599803201548</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -1261,7 +1261,7 @@
         <v>0.361671054226376</v>
       </c>
       <c r="P16">
-        <v>0.6317916594221523</v>
+        <v>0.4480900764878295</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -1311,7 +1311,7 @@
         <v>0.5575939890900888</v>
       </c>
       <c r="P17">
-        <v>0.5031098549517493</v>
+        <v>0.1323973302504604</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -1361,7 +1361,7 @@
         <v>0.2029753738572109</v>
       </c>
       <c r="P18">
-        <v>0.6317916594221523</v>
+        <v>0.3755214679878263</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -1411,7 +1411,7 @@
         <v>0.2984375450876925</v>
       </c>
       <c r="P19">
-        <v>0.009409586153315875</v>
+        <v>0.0004952413764903092</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -1461,7 +1461,7 @@
         <v>0.3751592015448161</v>
       </c>
       <c r="P20">
-        <v>0.6911994563077999</v>
+        <v>0.6199380522855404</v>
       </c>
     </row>
   </sheetData>
